--- a/03_Outputs/all/03_DS/ds_idx6_crecimiento.xlsx
+++ b/03_Outputs/all/03_DS/ds_idx6_crecimiento.xlsx
@@ -403,19 +403,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.2958798463172477</v>
+        <v>0.2958798463172449</v>
       </c>
       <c r="D2">
-        <v>3.267155713058323</v>
+        <v>3.26715571305832</v>
       </c>
       <c r="E2">
-        <v>-0.2678408117167195</v>
+        <v>-0.2678408117167158</v>
       </c>
       <c r="F2">
-        <v>0.1488596155285893</v>
+        <v>0.1488596155285882</v>
       </c>
       <c r="G2">
-        <v>0.2193159328506051</v>
+        <v>0.219315932850606</v>
       </c>
     </row>
     <row r="3">
@@ -430,19 +430,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>-0.5022802955158733</v>
+        <v>-0.5022802955158721</v>
       </c>
       <c r="D3">
-        <v>-1.360766542260433</v>
+        <v>-1.360766542260431</v>
       </c>
       <c r="E3">
-        <v>-0.6653062817641862</v>
+        <v>-0.6653062817641859</v>
       </c>
       <c r="F3">
-        <v>0.310325681620491</v>
+        <v>0.3103256816204907</v>
       </c>
       <c r="G3">
-        <v>0.04099782969575955</v>
+        <v>0.04099782969576243</v>
       </c>
     </row>
     <row r="4">
@@ -457,19 +457,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>-1.918675644842569</v>
+        <v>-1.91867564484257</v>
       </c>
       <c r="D4">
-        <v>0.4923940716166712</v>
+        <v>0.4923940716166678</v>
       </c>
       <c r="E4">
-        <v>2.112188518229273</v>
+        <v>2.112188518229276</v>
       </c>
       <c r="F4">
-        <v>1.087726885056682</v>
+        <v>1.087726885056685</v>
       </c>
       <c r="G4">
-        <v>-1.004683100870241</v>
+        <v>-1.004683100870239</v>
       </c>
     </row>
     <row r="5">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>-0.1706851197773043</v>
+        <v>-0.170685119777303</v>
       </c>
       <c r="D5">
-        <v>-0.7509381946347415</v>
+        <v>-0.7509381946347405</v>
       </c>
       <c r="E5">
-        <v>-0.5216810542074248</v>
+        <v>-0.5216810542074269</v>
       </c>
       <c r="F5">
-        <v>-0.7221059741116228</v>
+        <v>-0.7221059741116205</v>
       </c>
       <c r="G5">
-        <v>-0.3009298926638078</v>
+        <v>-0.3009298926638097</v>
       </c>
     </row>
     <row r="6">
@@ -511,19 +511,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>2.63581668255438</v>
+        <v>2.635816682554381</v>
       </c>
       <c r="D6">
-        <v>-0.6898376431480278</v>
+        <v>-0.689837643148026</v>
       </c>
       <c r="E6">
-        <v>-0.1121307438949901</v>
+        <v>-0.1121307438949892</v>
       </c>
       <c r="F6">
-        <v>0.6105283627637828</v>
+        <v>0.6105283627637799</v>
       </c>
       <c r="G6">
-        <v>1.002321780129167</v>
+        <v>1.002321780129168</v>
       </c>
     </row>
     <row r="7">
@@ -538,19 +538,19 @@
         </is>
       </c>
       <c r="C7">
-        <v>-0.9691611778580875</v>
+        <v>-0.9691611778580882</v>
       </c>
       <c r="D7">
-        <v>0.6703923134821824</v>
+        <v>0.6703923134821826</v>
       </c>
       <c r="E7">
-        <v>-0.2756996048172585</v>
+        <v>-0.2756996048172539</v>
       </c>
       <c r="F7">
-        <v>0.8619073359365327</v>
+        <v>0.8619073359365351</v>
       </c>
       <c r="G7">
-        <v>-0.3958271879369138</v>
+        <v>-0.395827187936909</v>
       </c>
     </row>
     <row r="8">
@@ -565,19 +565,19 @@
         </is>
       </c>
       <c r="C8">
-        <v>-0.2727552043832681</v>
+        <v>-0.2727552043832671</v>
       </c>
       <c r="D8">
-        <v>-0.02945312769330731</v>
+        <v>-0.02945312769330673</v>
       </c>
       <c r="E8">
-        <v>0.1657799692486348</v>
+        <v>0.1657799692486341</v>
       </c>
       <c r="F8">
-        <v>-0.640190130090762</v>
+        <v>-0.6401901300907641</v>
       </c>
       <c r="G8">
-        <v>0.1645180573001777</v>
+        <v>0.1645180573001767</v>
       </c>
     </row>
     <row r="9">
@@ -592,19 +592,19 @@
         </is>
       </c>
       <c r="C9">
-        <v>0.3668156323453559</v>
+        <v>0.3668156323453562</v>
       </c>
       <c r="D9">
-        <v>-0.7325858659317878</v>
+        <v>-0.7325858659317865</v>
       </c>
       <c r="E9">
-        <v>0.01135173148630598</v>
+        <v>0.0113517314863111</v>
       </c>
       <c r="F9">
         <v>1.59211633936023</v>
       </c>
       <c r="G9">
-        <v>-0.1647906536181052</v>
+        <v>-0.1647906536180961</v>
       </c>
     </row>
     <row r="10">
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>-1.13057940627499</v>
+        <v>-1.130579406274988</v>
       </c>
       <c r="D10">
         <v>-0.7979894355323783</v>
       </c>
       <c r="E10">
-        <v>0.4562731886446331</v>
+        <v>0.4562731886446289</v>
       </c>
       <c r="F10">
-        <v>-1.367918923601597</v>
+        <v>-1.367918923601604</v>
       </c>
       <c r="G10">
-        <v>1.274020380965588</v>
+        <v>1.274020380965583</v>
       </c>
     </row>
     <row r="11">
@@ -646,19 +646,19 @@
         </is>
       </c>
       <c r="C11">
-        <v>-1.408277582934246</v>
+        <v>-1.408277582934247</v>
       </c>
       <c r="D11">
-        <v>0.7101952169552678</v>
+        <v>0.710195216955268</v>
       </c>
       <c r="E11">
-        <v>-0.5039012421528126</v>
+        <v>-0.5039012421528091</v>
       </c>
       <c r="F11">
-        <v>0.4920753314123222</v>
+        <v>0.4920753314123233</v>
       </c>
       <c r="G11">
-        <v>0.07900958873808446</v>
+        <v>0.07900958873808732</v>
       </c>
     </row>
     <row r="12">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="C12">
-        <v>-0.004972271769738481</v>
+        <v>-0.004972271769738085</v>
       </c>
       <c r="D12">
-        <v>0.9126855515140729</v>
+        <v>0.9126855515140715</v>
       </c>
       <c r="E12">
-        <v>0.8112411657390655</v>
+        <v>0.8112411657390605</v>
       </c>
       <c r="F12">
-        <v>-1.99236191293284</v>
+        <v>-1.992361912932848</v>
       </c>
       <c r="G12">
-        <v>0.8627795951449257</v>
+        <v>0.8627795951449176</v>
       </c>
     </row>
     <row r="13">
@@ -700,19 +700,19 @@
         </is>
       </c>
       <c r="C13">
-        <v>0.07446463813027966</v>
+        <v>0.07446463813028058</v>
       </c>
       <c r="D13">
-        <v>-0.1216584653654079</v>
+        <v>-0.1216584653654077</v>
       </c>
       <c r="E13">
-        <v>-0.3357080360067363</v>
+        <v>-0.3357080360067402</v>
       </c>
       <c r="F13">
-        <v>-1.341106948714929</v>
+        <v>-1.341106948714932</v>
       </c>
       <c r="G13">
-        <v>1.196291387064542</v>
+        <v>1.196291387064534</v>
       </c>
     </row>
     <row r="14">
@@ -730,16 +730,16 @@
         <v>-1.010714668325656</v>
       </c>
       <c r="D14">
-        <v>0.8360726276325239</v>
+        <v>0.8360726276325231</v>
       </c>
       <c r="E14">
-        <v>0.07695178241298326</v>
+        <v>0.07695178241298188</v>
       </c>
       <c r="F14">
-        <v>-0.9307013503861382</v>
+        <v>-0.9307013503861378</v>
       </c>
       <c r="G14">
-        <v>0.1124223109567943</v>
+        <v>0.1124223109567892</v>
       </c>
     </row>
     <row r="15">
@@ -760,13 +760,13 @@
         <v>-1.144489843222168</v>
       </c>
       <c r="E15">
-        <v>-0.2337081606647849</v>
+        <v>-0.2337081606647853</v>
       </c>
       <c r="F15">
-        <v>0.2318429132142295</v>
+        <v>0.2318429132142287</v>
       </c>
       <c r="G15">
-        <v>0.3544184471052774</v>
+        <v>0.3544184471052777</v>
       </c>
     </row>
     <row r="16">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>-1.305267518026773</v>
+        <v>-1.305267518026771</v>
       </c>
       <c r="D16">
-        <v>-1.266974029266793</v>
+        <v>-1.266974029266792</v>
       </c>
       <c r="E16">
-        <v>-1.656624166986282</v>
+        <v>-1.65662416698629</v>
       </c>
       <c r="F16">
-        <v>-2.232357424674535</v>
+        <v>-2.232357424674523</v>
       </c>
       <c r="G16">
-        <v>-0.9300003898444952</v>
+        <v>-0.9300003898445082</v>
       </c>
     </row>
     <row r="17">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C17">
-        <v>-1.170475624268124</v>
+        <v>-1.170475624268126</v>
       </c>
       <c r="D17">
-        <v>-0.7963594006790233</v>
+        <v>-0.7963594006790324</v>
       </c>
       <c r="E17">
-        <v>6.461274788382817</v>
+        <v>6.46127478838281</v>
       </c>
       <c r="F17">
-        <v>-0.1683380566182215</v>
+        <v>-0.1683380566182193</v>
       </c>
       <c r="G17">
-        <v>-2.442069483216058</v>
+        <v>-2.442069483216067</v>
       </c>
     </row>
     <row r="18">
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="C18">
-        <v>2.462125651919482</v>
+        <v>2.462125651919481</v>
       </c>
       <c r="D18">
-        <v>1.021991186651109</v>
+        <v>1.021991186651108</v>
       </c>
       <c r="E18">
-        <v>-0.4638534448969012</v>
+        <v>-0.4638534448968971</v>
       </c>
       <c r="F18">
-        <v>1.199843430800355</v>
+        <v>1.199843430800352</v>
       </c>
       <c r="G18">
-        <v>1.111325746682471</v>
+        <v>1.111325746682474</v>
       </c>
     </row>
     <row r="19">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="C19">
-        <v>-0.6663996667321856</v>
+        <v>-0.6663996667321859</v>
       </c>
       <c r="D19">
-        <v>-0.1741735326708855</v>
+        <v>-0.1741735326708852</v>
       </c>
       <c r="E19">
-        <v>-0.2203578000389186</v>
+        <v>-0.2203578000389127</v>
       </c>
       <c r="F19">
-        <v>1.714400544313578</v>
+        <v>1.714400544313579</v>
       </c>
       <c r="G19">
-        <v>-0.03371957783722838</v>
+        <v>-0.03371957783721921</v>
       </c>
     </row>
     <row r="20">
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="C20">
-        <v>-0.3304195400943563</v>
+        <v>-0.3304195400943568</v>
       </c>
       <c r="D20">
-        <v>1.277807576519732</v>
+        <v>1.27780757651973</v>
       </c>
       <c r="E20">
-        <v>-0.6786597678888945</v>
+        <v>-0.6786597678888923</v>
       </c>
       <c r="F20">
-        <v>0.1318401228972763</v>
+        <v>0.1318401228972756</v>
       </c>
       <c r="G20">
-        <v>0.1569537500022015</v>
+        <v>0.1569537500022044</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="C21">
-        <v>1.521098781279371</v>
+        <v>1.521098781279372</v>
       </c>
       <c r="D21">
-        <v>-1.946862535864202</v>
+        <v>-1.946862535864199</v>
       </c>
       <c r="E21">
-        <v>-0.1974687519122606</v>
+        <v>-0.19746875191226</v>
       </c>
       <c r="F21">
-        <v>0.5566716505501388</v>
+        <v>0.5566716505501403</v>
       </c>
       <c r="G21">
-        <v>0.2673070907742048</v>
+        <v>0.2673070907742064</v>
       </c>
     </row>
     <row r="22">
@@ -943,19 +943,19 @@
         </is>
       </c>
       <c r="C22">
-        <v>0.7160692807006728</v>
+        <v>0.7160692807006745</v>
       </c>
       <c r="D22">
-        <v>-1.517564571237353</v>
+        <v>-1.517564571237352</v>
       </c>
       <c r="E22">
-        <v>0.1135254004252743</v>
+        <v>0.1135254004252742</v>
       </c>
       <c r="F22">
-        <v>0.4071659614418729</v>
+        <v>0.4071659614418673</v>
       </c>
       <c r="G22">
-        <v>0.1273698876395994</v>
+        <v>0.1273698876396053</v>
       </c>
     </row>
     <row r="23">
@@ -970,16 +970,16 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.1285221766169402</v>
+        <v>0.1285221766169401</v>
       </c>
       <c r="D23">
-        <v>0.4084251901361628</v>
+        <v>0.4084251901361622</v>
       </c>
       <c r="E23">
-        <v>0.3909489281035957</v>
+        <v>0.3909489281035963</v>
       </c>
       <c r="F23">
-        <v>-0.01989554676511989</v>
+        <v>-0.01989554676512206</v>
       </c>
       <c r="G23">
         <v>0.2605455064921851</v>
@@ -997,19 +997,19 @@
         </is>
       </c>
       <c r="C24">
-        <v>-0.8555624387529061</v>
+        <v>-0.8555624387529057</v>
       </c>
       <c r="D24">
-        <v>-0.9326364004381883</v>
+        <v>-0.9326364004381872</v>
       </c>
       <c r="E24">
-        <v>-0.3594244349486955</v>
+        <v>-0.3594244349486929</v>
       </c>
       <c r="F24">
-        <v>1.055536701931034</v>
+        <v>1.055536701931035</v>
       </c>
       <c r="G24">
-        <v>0.3260969966212737</v>
+        <v>0.326096996621277</v>
       </c>
     </row>
     <row r="25">
@@ -1027,16 +1027,16 @@
         <v>-1.386218357287726</v>
       </c>
       <c r="D25">
-        <v>0.1697763370420157</v>
+        <v>0.1697763370420165</v>
       </c>
       <c r="E25">
-        <v>-0.9645252066600926</v>
+        <v>-0.9645252066600905</v>
       </c>
       <c r="F25">
-        <v>0.4871226245102637</v>
+        <v>0.4871226245102723</v>
       </c>
       <c r="G25">
-        <v>-0.5770157086811118</v>
+        <v>-0.577015708681112</v>
       </c>
     </row>
     <row r="26">
@@ -1051,19 +1051,19 @@
         </is>
       </c>
       <c r="C26">
-        <v>-1.760365538976434</v>
+        <v>-1.760365538976435</v>
       </c>
       <c r="D26">
-        <v>-0.1523906994658512</v>
+        <v>-0.1523906994658508</v>
       </c>
       <c r="E26">
-        <v>-1.391196138552818</v>
+        <v>-1.391196138552816</v>
       </c>
       <c r="F26">
-        <v>0.7236599431198473</v>
+        <v>0.7236599431198524</v>
       </c>
       <c r="G26">
-        <v>0.1652411998386212</v>
+        <v>0.1652411998386233</v>
       </c>
     </row>
     <row r="27">
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="C27">
-        <v>-0.4609937588461543</v>
+        <v>-0.4609937588461522</v>
       </c>
       <c r="D27">
-        <v>-1.111419145165068</v>
+        <v>-1.111419145165067</v>
       </c>
       <c r="E27">
-        <v>0.1946039600694188</v>
+        <v>0.1946039600694126</v>
       </c>
       <c r="F27">
-        <v>-1.892569054008016</v>
+        <v>-1.89256905400802</v>
       </c>
       <c r="G27">
-        <v>0.315910578114621</v>
+        <v>0.3159105781146141</v>
       </c>
     </row>
     <row r="28">
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="C28">
-        <v>1.654499621171786</v>
+        <v>1.654499621171785</v>
       </c>
       <c r="D28">
-        <v>1.684091327346784</v>
+        <v>1.684091327346782</v>
       </c>
       <c r="E28">
-        <v>0.03891869052449098</v>
+        <v>0.03891869052449337</v>
       </c>
       <c r="F28">
-        <v>0.2728695692019241</v>
+        <v>0.2728695692019169</v>
       </c>
       <c r="G28">
-        <v>0.9618215060684897</v>
+        <v>0.9618215060684924</v>
       </c>
     </row>
     <row r="29">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="C29">
-        <v>-0.6309996656118817</v>
+        <v>-0.6309996656118793</v>
       </c>
       <c r="D29">
         <v>-1.583138525983667</v>
       </c>
       <c r="E29">
-        <v>1.102877865287021</v>
+        <v>1.102877865287015</v>
       </c>
       <c r="F29">
-        <v>-1.665477270936821</v>
+        <v>-1.665477270936832</v>
       </c>
       <c r="G29">
-        <v>1.442361690556504</v>
+        <v>1.442361690556499</v>
       </c>
     </row>
     <row r="30">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="C30">
-        <v>0.1967766363842701</v>
+        <v>0.1967766363842703</v>
       </c>
       <c r="D30">
-        <v>-0.0996586857222042</v>
+        <v>-0.09965868572220471</v>
       </c>
       <c r="E30">
-        <v>0.3189528375065468</v>
+        <v>0.3189528375065465</v>
       </c>
       <c r="F30">
-        <v>-0.05111022547954513</v>
+        <v>-0.05111022547955215</v>
       </c>
       <c r="G30">
-        <v>1.365270994698334</v>
+        <v>1.365270994698333</v>
       </c>
     </row>
     <row r="31">
@@ -1189,16 +1189,16 @@
         <v>-1.442631649679057</v>
       </c>
       <c r="D31">
-        <v>0.4716857928831286</v>
+        <v>0.4716857928831282</v>
       </c>
       <c r="E31">
-        <v>0.6846677806451595</v>
+        <v>0.6846677806451605</v>
       </c>
       <c r="F31">
-        <v>0.1380575485062309</v>
+        <v>0.1380575485062322</v>
       </c>
       <c r="G31">
-        <v>-0.4496595402518888</v>
+        <v>-0.4496595402518897</v>
       </c>
     </row>
     <row r="32">
@@ -1213,19 +1213,19 @@
         </is>
       </c>
       <c r="C32">
-        <v>0.5550009738379149</v>
+        <v>0.5550009738379157</v>
       </c>
       <c r="D32">
-        <v>-0.5037024553400427</v>
+        <v>-0.5037024553400442</v>
       </c>
       <c r="E32">
-        <v>1.408758666021869</v>
+        <v>1.408758666021864</v>
       </c>
       <c r="F32">
-        <v>-1.206100010900102</v>
+        <v>-1.206100010900113</v>
       </c>
       <c r="G32">
-        <v>1.246125639894045</v>
+        <v>1.246125639894039</v>
       </c>
     </row>
     <row r="33">
@@ -1240,19 +1240,19 @@
         </is>
       </c>
       <c r="C33">
-        <v>-0.7026877372980604</v>
+        <v>-0.7026877372980599</v>
       </c>
       <c r="D33">
-        <v>-0.08185101179957716</v>
+        <v>-0.08185101179957767</v>
       </c>
       <c r="E33">
-        <v>0.0655302195575708</v>
+        <v>0.06553021955756834</v>
       </c>
       <c r="F33">
-        <v>-0.815320974246706</v>
+        <v>-0.8153209742467054</v>
       </c>
       <c r="G33">
-        <v>-0.1391385755248734</v>
+        <v>-0.1391385755248769</v>
       </c>
     </row>
     <row r="34">
@@ -1267,19 +1267,19 @@
         </is>
       </c>
       <c r="C34">
-        <v>0.5728988540340774</v>
+        <v>0.5728988540340779</v>
       </c>
       <c r="D34">
-        <v>0.9558793145221396</v>
+        <v>0.9558793145221409</v>
       </c>
       <c r="E34">
-        <v>-1.870166662437619</v>
+        <v>-1.87016666243762</v>
       </c>
       <c r="F34">
-        <v>-0.8871985692180131</v>
+        <v>-0.8871985692180014</v>
       </c>
       <c r="G34">
-        <v>-1.035199029282547</v>
+        <v>-1.035199029282549</v>
       </c>
     </row>
     <row r="35">
@@ -1294,19 +1294,19 @@
         </is>
       </c>
       <c r="C35">
-        <v>-0.3698416230652207</v>
+        <v>-0.3698416230652204</v>
       </c>
       <c r="D35">
-        <v>-0.3569733892011194</v>
+        <v>-0.3569733892011203</v>
       </c>
       <c r="E35">
-        <v>0.5162415837189337</v>
+        <v>0.5162415837189365</v>
       </c>
       <c r="F35">
-        <v>0.9366965093195376</v>
+        <v>0.9366965093195374</v>
       </c>
       <c r="G35">
-        <v>-1.031523729625798</v>
+        <v>-1.03152372962579</v>
       </c>
     </row>
     <row r="36">
@@ -1321,19 +1321,19 @@
         </is>
       </c>
       <c r="C36">
-        <v>-0.8867202826128137</v>
+        <v>-0.8867202826128145</v>
       </c>
       <c r="D36">
-        <v>1.095617985403422</v>
+        <v>1.09561798540342</v>
       </c>
       <c r="E36">
-        <v>0.4415502942353189</v>
+        <v>0.4415502942353173</v>
       </c>
       <c r="F36">
-        <v>-0.7169333483298646</v>
+        <v>-0.716933348329864</v>
       </c>
       <c r="G36">
-        <v>0.01207579120702318</v>
+        <v>0.01207579120701809</v>
       </c>
     </row>
     <row r="37">
@@ -1351,16 +1351,16 @@
         <v>-1.338716888324179</v>
       </c>
       <c r="D37">
-        <v>0.455995143447335</v>
+        <v>0.4559951434473348</v>
       </c>
       <c r="E37">
-        <v>-0.8526637946483356</v>
+        <v>-0.8526637946483354</v>
       </c>
       <c r="F37">
-        <v>-0.1930510176594584</v>
+        <v>-0.1930510176594551</v>
       </c>
       <c r="G37">
-        <v>0.2219499547882124</v>
+        <v>0.2219499547882096</v>
       </c>
     </row>
     <row r="38">
@@ -1375,19 +1375,19 @@
         </is>
       </c>
       <c r="C38">
-        <v>1.571298112992868</v>
+        <v>1.571298112992867</v>
       </c>
       <c r="D38">
-        <v>2.071677997171687</v>
+        <v>2.071677997171685</v>
       </c>
       <c r="E38">
-        <v>1.96235607652906</v>
+        <v>1.962356076529056</v>
       </c>
       <c r="F38">
-        <v>-1.963873159120914</v>
+        <v>-1.963873159120921</v>
       </c>
       <c r="G38">
-        <v>0.7192376064237886</v>
+        <v>0.7192376064237781</v>
       </c>
     </row>
     <row r="39">
@@ -1402,19 +1402,19 @@
         </is>
       </c>
       <c r="C39">
-        <v>-0.1534641156428318</v>
+        <v>-0.1534641156428316</v>
       </c>
       <c r="D39">
-        <v>-0.05522449959906245</v>
+        <v>-0.05522449959906205</v>
       </c>
       <c r="E39">
-        <v>-1.236251798106266</v>
+        <v>-1.236251798106268</v>
       </c>
       <c r="F39">
-        <v>-0.6955808273069116</v>
+        <v>-0.6955808273069037</v>
       </c>
       <c r="G39">
-        <v>-0.5734663539454321</v>
+        <v>-0.573466353945437</v>
       </c>
     </row>
     <row r="40">
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="C40">
-        <v>-0.8641116885329362</v>
+        <v>-0.8641116885329356</v>
       </c>
       <c r="D40">
-        <v>-0.6412698857750545</v>
+        <v>-0.6412698857750547</v>
       </c>
       <c r="E40">
-        <v>-0.175917556832308</v>
+        <v>-0.1759175568323111</v>
       </c>
       <c r="F40">
-        <v>-0.5844146372605541</v>
+        <v>-0.584414637260548</v>
       </c>
       <c r="G40">
-        <v>-1.141208358687733</v>
+        <v>-1.141208358687736</v>
       </c>
     </row>
     <row r="41">
@@ -1462,13 +1462,13 @@
         <v>-1.538603903575446</v>
       </c>
       <c r="E41">
-        <v>-0.1644225642496844</v>
+        <v>-0.1644225642496806</v>
       </c>
       <c r="F41">
-        <v>2.028675186038902</v>
+        <v>2.028675186038898</v>
       </c>
       <c r="G41">
-        <v>0.4534834686108903</v>
+        <v>0.4534834686109003</v>
       </c>
     </row>
     <row r="42">
@@ -1483,19 +1483,19 @@
         </is>
       </c>
       <c r="C42">
-        <v>1.186093350155435</v>
+        <v>1.186093350155432</v>
       </c>
       <c r="D42">
-        <v>2.576947096223791</v>
+        <v>2.576947096223788</v>
       </c>
       <c r="E42">
-        <v>-0.2748907749351996</v>
+        <v>-0.2748907749351974</v>
       </c>
       <c r="F42">
-        <v>0.3612484009140553</v>
+        <v>0.3612484009140441</v>
       </c>
       <c r="G42">
-        <v>1.853699938312722</v>
+        <v>1.853699938312723</v>
       </c>
     </row>
     <row r="43">
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="C43">
-        <v>-1.77361098905687</v>
+        <v>-1.773610989056868</v>
       </c>
       <c r="D43">
         <v>-0.5125389019099995</v>
       </c>
       <c r="E43">
-        <v>-0.1439721650361186</v>
+        <v>-0.1439721650361272</v>
       </c>
       <c r="F43">
-        <v>-2.931622916185484</v>
+        <v>-2.931622916185492</v>
       </c>
       <c r="G43">
-        <v>1.382179884588258</v>
+        <v>1.382179884588246</v>
       </c>
     </row>
     <row r="44">
@@ -1540,16 +1540,16 @@
         <v>1.250995296737662</v>
       </c>
       <c r="D44">
-        <v>0.7613211692068595</v>
+        <v>0.7613211692068604</v>
       </c>
       <c r="E44">
-        <v>-0.05881997281962444</v>
+        <v>-0.05881997281962152</v>
       </c>
       <c r="F44">
-        <v>0.3527696192253016</v>
+        <v>0.352769619225305</v>
       </c>
       <c r="G44">
-        <v>-0.347605219296804</v>
+        <v>-0.3476052192968027</v>
       </c>
     </row>
     <row r="45">
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="C45">
-        <v>-0.3560060701472763</v>
+        <v>-0.3560060701472759</v>
       </c>
       <c r="D45">
-        <v>-0.6642868736979568</v>
+        <v>-0.6642868736979562</v>
       </c>
       <c r="E45">
-        <v>0.1970715405549257</v>
+        <v>0.1970715405549284</v>
       </c>
       <c r="F45">
-        <v>0.9288598919693084</v>
+        <v>0.9288598919693078</v>
       </c>
       <c r="G45">
-        <v>0.02853822403377699</v>
+        <v>0.0285382240337817</v>
       </c>
     </row>
     <row r="46">
@@ -1594,16 +1594,16 @@
         <v>-1.749078249654259</v>
       </c>
       <c r="D46">
-        <v>0.7766893096575991</v>
+        <v>0.7766893096575981</v>
       </c>
       <c r="E46">
-        <v>0.01916262230446485</v>
+        <v>0.01916262230446518</v>
       </c>
       <c r="F46">
-        <v>-0.3846879894764291</v>
+        <v>-0.3846879894764277</v>
       </c>
       <c r="G46">
-        <v>0.03011475391290324</v>
+        <v>0.03011475391290102</v>
       </c>
     </row>
     <row r="47">
@@ -1618,19 +1618,19 @@
         </is>
       </c>
       <c r="C47">
-        <v>0.4979012007102471</v>
+        <v>0.4979012007102468</v>
       </c>
       <c r="D47">
         <v>0.7853928880115483</v>
       </c>
       <c r="E47">
-        <v>0.03311449240615734</v>
+        <v>0.03311449240616265</v>
       </c>
       <c r="F47">
-        <v>1.03142691757908</v>
+        <v>1.031426917579083</v>
       </c>
       <c r="G47">
-        <v>-0.8567821065488013</v>
+        <v>-0.8567821065487937</v>
       </c>
     </row>
     <row r="48">
@@ -1645,19 +1645,19 @@
         </is>
       </c>
       <c r="C48">
-        <v>0.4023499534924379</v>
+        <v>0.4023499534924354</v>
       </c>
       <c r="D48">
-        <v>3.928417739895965</v>
+        <v>3.928417739895963</v>
       </c>
       <c r="E48">
-        <v>-0.9269898470526448</v>
+        <v>-0.9269898470526388</v>
       </c>
       <c r="F48">
-        <v>0.3042268625372813</v>
+        <v>0.3042268625372824</v>
       </c>
       <c r="G48">
-        <v>0.1857157832213932</v>
+        <v>0.1857157832213955</v>
       </c>
     </row>
     <row r="49">
@@ -1672,19 +1672,19 @@
         </is>
       </c>
       <c r="C49">
-        <v>0.4830578899222552</v>
+        <v>0.4830578899222558</v>
       </c>
       <c r="D49">
-        <v>-1.158054810512974</v>
+        <v>-1.158054810512972</v>
       </c>
       <c r="E49">
-        <v>-0.3383553774946305</v>
+        <v>-0.3383553774946244</v>
       </c>
       <c r="F49">
         <v>2.070352250247774</v>
       </c>
       <c r="G49">
-        <v>-0.2772841433786207</v>
+        <v>-0.2772841433786091</v>
       </c>
     </row>
     <row r="50">
@@ -1699,19 +1699,19 @@
         </is>
       </c>
       <c r="C50">
-        <v>-2.054115697920058</v>
+        <v>-2.054115697920057</v>
       </c>
       <c r="D50">
-        <v>-0.06408202919061573</v>
+        <v>-0.06408202919061606</v>
       </c>
       <c r="E50">
-        <v>-0.1584868195799767</v>
+        <v>-0.1584868195799768</v>
       </c>
       <c r="F50">
-        <v>-0.211258044914247</v>
+        <v>-0.2112580449142494</v>
       </c>
       <c r="G50">
-        <v>0.4952292243746141</v>
+        <v>0.4952292243746135</v>
       </c>
     </row>
     <row r="51">
@@ -1726,19 +1726,19 @@
         </is>
       </c>
       <c r="C51">
-        <v>1.333409273272635</v>
+        <v>1.333409273272633</v>
       </c>
       <c r="D51">
-        <v>1.264109097196125</v>
+        <v>1.264109097196123</v>
       </c>
       <c r="E51">
-        <v>0.08464046577899073</v>
+        <v>0.08464046577899226</v>
       </c>
       <c r="F51">
-        <v>0.9240228836168113</v>
+        <v>0.9240228836168081</v>
       </c>
       <c r="G51">
-        <v>1.366407893250483</v>
+        <v>1.36640789325048</v>
       </c>
     </row>
     <row r="52">
@@ -1753,19 +1753,19 @@
         </is>
       </c>
       <c r="C52">
-        <v>-0.3989310063930624</v>
+        <v>-0.3989310063930632</v>
       </c>
       <c r="D52">
-        <v>2.150830887551964</v>
+        <v>2.150830887551962</v>
       </c>
       <c r="E52">
-        <v>-0.6408155288722588</v>
+        <v>-0.6408155288722581</v>
       </c>
       <c r="F52">
-        <v>-0.7585576912019811</v>
+        <v>-0.7585576912019834</v>
       </c>
       <c r="G52">
-        <v>0.7675844709068738</v>
+        <v>0.7675844709068712</v>
       </c>
     </row>
     <row r="53">
@@ -1783,16 +1783,16 @@
         <v>-1.072792828720841</v>
       </c>
       <c r="D53">
-        <v>-0.0469477806047192</v>
+        <v>-0.04694778060471948</v>
       </c>
       <c r="E53">
-        <v>0.1354198988324047</v>
+        <v>0.1354198988324063</v>
       </c>
       <c r="F53">
-        <v>0.305779859036086</v>
+        <v>0.3057798590360852</v>
       </c>
       <c r="G53">
-        <v>-0.08247772828281055</v>
+        <v>-0.08247772828280822</v>
       </c>
     </row>
     <row r="54">
@@ -1807,19 +1807,19 @@
         </is>
       </c>
       <c r="C54">
-        <v>0.3093314067497793</v>
+        <v>0.3093314067497809</v>
       </c>
       <c r="D54">
-        <v>-2.113980035629695</v>
+        <v>-2.113980035629694</v>
       </c>
       <c r="E54">
-        <v>0.1498964696275333</v>
+        <v>0.1498964696275288</v>
       </c>
       <c r="F54">
-        <v>-0.4286711306109985</v>
+        <v>-0.4286711306109923</v>
       </c>
       <c r="G54">
-        <v>-0.6304987769575808</v>
+        <v>-0.6304987769575858</v>
       </c>
     </row>
     <row r="55">
@@ -1834,19 +1834,19 @@
         </is>
       </c>
       <c r="C55">
-        <v>-0.6875551865303333</v>
+        <v>-0.6875551865303323</v>
       </c>
       <c r="D55">
-        <v>-1.126582018531584</v>
+        <v>-1.126582018531583</v>
       </c>
       <c r="E55">
-        <v>0.1775679760985384</v>
+        <v>0.177567976098539</v>
       </c>
       <c r="F55">
-        <v>0.3506137310358132</v>
+        <v>0.3506137310358101</v>
       </c>
       <c r="G55">
-        <v>0.784648195957606</v>
+        <v>0.784648195957607</v>
       </c>
     </row>
     <row r="56">
@@ -1861,19 +1861,19 @@
         </is>
       </c>
       <c r="C56">
-        <v>4.776935855782131</v>
+        <v>4.776935855782132</v>
       </c>
       <c r="D56">
-        <v>-1.344037548596273</v>
+        <v>-1.344037548596269</v>
       </c>
       <c r="E56">
-        <v>-1.559658067597483</v>
+        <v>-1.559658067597484</v>
       </c>
       <c r="F56">
-        <v>0.0379175822490418</v>
+        <v>0.03791758224905289</v>
       </c>
       <c r="G56">
-        <v>-0.1523885560586182</v>
+        <v>-0.1523885560586226</v>
       </c>
     </row>
     <row r="57">
@@ -1891,16 +1891,16 @@
         <v>2.192010414331297</v>
       </c>
       <c r="D57">
-        <v>1.536793410689454</v>
+        <v>1.536793410689453</v>
       </c>
       <c r="E57">
-        <v>-0.1339194334316116</v>
+        <v>-0.133919433431615</v>
       </c>
       <c r="F57">
-        <v>-1.324758319332524</v>
+        <v>-1.324758319332498</v>
       </c>
       <c r="G57">
-        <v>-5.395925562080973</v>
+        <v>-5.395925562080977</v>
       </c>
     </row>
     <row r="58">
@@ -1915,19 +1915,19 @@
         </is>
       </c>
       <c r="C58">
-        <v>0.3622196101090198</v>
+        <v>0.3622196101090215</v>
       </c>
       <c r="D58">
         <v>-1.377850000045386</v>
       </c>
       <c r="E58">
-        <v>0.6257064457010548</v>
+        <v>0.6257064457010568</v>
       </c>
       <c r="F58">
-        <v>0.7625606979863003</v>
+        <v>0.7625606979862923</v>
       </c>
       <c r="G58">
-        <v>0.0149350790656764</v>
+        <v>0.01493507906568584</v>
       </c>
     </row>
     <row r="59">
@@ -1942,19 +1942,19 @@
         </is>
       </c>
       <c r="C59">
-        <v>0.4762414418256465</v>
+        <v>0.476241441825647</v>
       </c>
       <c r="D59">
-        <v>-0.9237343285361649</v>
+        <v>-0.9237343285361639</v>
       </c>
       <c r="E59">
-        <v>0.2956373443574701</v>
+        <v>0.2956373443574711</v>
       </c>
       <c r="F59">
-        <v>0.7901087340162306</v>
+        <v>0.7901087340162363</v>
       </c>
       <c r="G59">
-        <v>-0.7652243857661059</v>
+        <v>-0.765224385766104</v>
       </c>
     </row>
     <row r="60">
@@ -1969,19 +1969,19 @@
         </is>
       </c>
       <c r="C60">
-        <v>4.250224679736363</v>
+        <v>4.250224679736362</v>
       </c>
       <c r="D60">
-        <v>2.847057126086519</v>
+        <v>2.847057126086517</v>
       </c>
       <c r="E60">
-        <v>-0.2758256777294145</v>
+        <v>-0.2758256777294124</v>
       </c>
       <c r="F60">
-        <v>0.1531681030614525</v>
+        <v>0.1531681030614473</v>
       </c>
       <c r="G60">
-        <v>1.99203278747253</v>
+        <v>1.992032787472526</v>
       </c>
     </row>
     <row r="61">
@@ -1996,19 +1996,19 @@
         </is>
       </c>
       <c r="C61">
-        <v>-2.835069091117661</v>
+        <v>-2.835069091117662</v>
       </c>
       <c r="D61">
-        <v>-0.5222305433169391</v>
+        <v>-0.5222305433169383</v>
       </c>
       <c r="E61">
-        <v>-1.12083321138367</v>
+        <v>-1.120833211383669</v>
       </c>
       <c r="F61">
-        <v>0.3297180375612886</v>
+        <v>0.3297180375612884</v>
       </c>
       <c r="G61">
-        <v>0.785562879692346</v>
+        <v>0.7855628796923465</v>
       </c>
     </row>
     <row r="62">
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="C62">
-        <v>0.7234494941365409</v>
+        <v>0.7234494941365414</v>
       </c>
       <c r="D62">
-        <v>0.4879338019178801</v>
+        <v>0.4879338019178813</v>
       </c>
       <c r="E62">
-        <v>-0.1854849863480014</v>
+        <v>-0.1854849863480002</v>
       </c>
       <c r="F62">
-        <v>-0.1878518865109464</v>
+        <v>-0.187851886510941</v>
       </c>
       <c r="G62">
-        <v>-1.144987696560231</v>
+        <v>-1.14498769656023</v>
       </c>
     </row>
     <row r="63">
@@ -2053,16 +2053,16 @@
         <v>2.080250772517053</v>
       </c>
       <c r="D63">
-        <v>-0.2305387961013973</v>
+        <v>-0.2305387961013977</v>
       </c>
       <c r="E63">
-        <v>1.325054976058165</v>
+        <v>1.325054976058168</v>
       </c>
       <c r="F63">
-        <v>1.089268092503915</v>
+        <v>1.089268092503912</v>
       </c>
       <c r="G63">
-        <v>-0.5280837728008695</v>
+        <v>-0.5280837728008626</v>
       </c>
     </row>
     <row r="64">
@@ -2077,19 +2077,19 @@
         </is>
       </c>
       <c r="C64">
-        <v>3.680979373067331</v>
+        <v>3.680979373067332</v>
       </c>
       <c r="D64">
-        <v>-0.2718922047057454</v>
+        <v>-0.2718922047057434</v>
       </c>
       <c r="E64">
-        <v>0.005545305285638806</v>
+        <v>0.005545305285635987</v>
       </c>
       <c r="F64">
-        <v>-0.9317070488737546</v>
+        <v>-0.931707048873748</v>
       </c>
       <c r="G64">
-        <v>-0.6875400901006945</v>
+        <v>-0.6875400901006995</v>
       </c>
     </row>
     <row r="65">
@@ -2104,19 +2104,19 @@
         </is>
       </c>
       <c r="C65">
-        <v>0.493710717453367</v>
+        <v>0.4937107174533649</v>
       </c>
       <c r="D65">
-        <v>2.576065746739314</v>
+        <v>2.576065746739312</v>
       </c>
       <c r="E65">
-        <v>-0.6633303743073895</v>
+        <v>-0.6633303743073831</v>
       </c>
       <c r="F65">
-        <v>1.232121978445051</v>
+        <v>1.232121978445048</v>
       </c>
       <c r="G65">
-        <v>0.2969040869525917</v>
+        <v>0.2969040869526</v>
       </c>
     </row>
     <row r="66">
@@ -2131,19 +2131,19 @@
         </is>
       </c>
       <c r="C66">
-        <v>1.4250396261653</v>
+        <v>1.425039626165297</v>
       </c>
       <c r="D66">
-        <v>2.282254637056218</v>
+        <v>2.282254637056211</v>
       </c>
       <c r="E66">
-        <v>2.554265109630662</v>
+        <v>2.554265109630655</v>
       </c>
       <c r="F66">
-        <v>-1.720638346521183</v>
+        <v>-1.720638346521205</v>
       </c>
       <c r="G66">
-        <v>2.703772775243449</v>
+        <v>2.703772775243438</v>
       </c>
     </row>
     <row r="67">
@@ -2158,19 +2158,19 @@
         </is>
       </c>
       <c r="C67">
-        <v>1.758455511023867</v>
+        <v>1.75845551102387</v>
       </c>
       <c r="D67">
-        <v>-1.795935962332651</v>
+        <v>-1.795935962332649</v>
       </c>
       <c r="E67">
-        <v>-0.5960451200979179</v>
+        <v>-0.5960451200979253</v>
       </c>
       <c r="F67">
-        <v>-1.507505628177657</v>
+        <v>-1.507505628177652</v>
       </c>
       <c r="G67">
-        <v>0.1728751200546005</v>
+        <v>0.1728751200545896</v>
       </c>
     </row>
     <row r="68">
@@ -2185,19 +2185,19 @@
         </is>
       </c>
       <c r="C68">
-        <v>0.8893247500061817</v>
+        <v>0.8893247500061832</v>
       </c>
       <c r="D68">
-        <v>-0.8650636647811319</v>
+        <v>-0.8650636647811314</v>
       </c>
       <c r="E68">
-        <v>0.6192237120143355</v>
+        <v>0.6192237120143356</v>
       </c>
       <c r="F68">
-        <v>0.05278886931233856</v>
+        <v>0.05278886931233705</v>
       </c>
       <c r="G68">
-        <v>-0.1486327034221681</v>
+        <v>-0.1486327034221658</v>
       </c>
     </row>
     <row r="69">
@@ -2212,19 +2212,19 @@
         </is>
       </c>
       <c r="C69">
-        <v>-0.05049125516179427</v>
+        <v>-0.05049125516179601</v>
       </c>
       <c r="D69">
-        <v>1.438153983462879</v>
+        <v>1.438153983462878</v>
       </c>
       <c r="E69">
-        <v>1.002892207244429</v>
+        <v>1.002892207244431</v>
       </c>
       <c r="F69">
-        <v>0.4819518640634634</v>
+        <v>0.4819518640634639</v>
       </c>
       <c r="G69">
-        <v>-0.3326771374363344</v>
+        <v>-0.3326771374363349</v>
       </c>
     </row>
     <row r="70">
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="C70">
-        <v>4.281611713746706</v>
+        <v>4.281611713746709</v>
       </c>
       <c r="D70">
-        <v>-1.020984000386175</v>
+        <v>-1.020984000386171</v>
       </c>
       <c r="E70">
-        <v>-1.274470972299073</v>
+        <v>-1.274470972299078</v>
       </c>
       <c r="F70">
-        <v>-1.747994771446592</v>
+        <v>-1.747994771446582</v>
       </c>
       <c r="G70">
-        <v>-0.620143715761731</v>
+        <v>-0.620143715761739</v>
       </c>
     </row>
     <row r="71">
@@ -2266,19 +2266,19 @@
         </is>
       </c>
       <c r="C71">
-        <v>2.242859823381929</v>
+        <v>2.242859823381933</v>
       </c>
       <c r="D71">
-        <v>-3.287441387488941</v>
+        <v>-3.28744138748894</v>
       </c>
       <c r="E71">
-        <v>2.120436358831204</v>
+        <v>2.120436358831201</v>
       </c>
       <c r="F71">
-        <v>0.1942736778769955</v>
+        <v>0.1942736778769827</v>
       </c>
       <c r="G71">
-        <v>0.1331946727915988</v>
+        <v>0.1331946727916052</v>
       </c>
     </row>
     <row r="72">
@@ -2296,16 +2296,16 @@
         <v>-3.102969078155422</v>
       </c>
       <c r="D72">
-        <v>-0.6173575482112967</v>
+        <v>-0.6173575482112965</v>
       </c>
       <c r="E72">
         <v>-1.310166564336576</v>
       </c>
       <c r="F72">
-        <v>0.2999511716822663</v>
+        <v>0.2999511716822714</v>
       </c>
       <c r="G72">
-        <v>0.1043963769253152</v>
+        <v>0.1043963769253135</v>
       </c>
     </row>
     <row r="73">
@@ -2323,16 +2323,16 @@
         <v>-2.104449254414968</v>
       </c>
       <c r="D73">
-        <v>-0.07505528865848544</v>
+        <v>-0.07505528865848721</v>
       </c>
       <c r="E73">
-        <v>0.5664089637935423</v>
+        <v>0.5664089637935392</v>
       </c>
       <c r="F73">
         <v>-0.5574965878163662</v>
       </c>
       <c r="G73">
-        <v>0.02284659472536247</v>
+        <v>0.02284659472535697</v>
       </c>
     </row>
     <row r="74">
@@ -2347,19 +2347,19 @@
         </is>
       </c>
       <c r="C74">
-        <v>-1.388104141366115</v>
+        <v>-1.388104141366114</v>
       </c>
       <c r="D74">
-        <v>-1.569090912305975</v>
+        <v>-1.569090912305974</v>
       </c>
       <c r="E74">
-        <v>-1.673830034344836</v>
+        <v>-1.673830034344842</v>
       </c>
       <c r="F74">
-        <v>-1.035446615678755</v>
+        <v>-1.035446615678744</v>
       </c>
       <c r="G74">
-        <v>-0.9945391869010903</v>
+        <v>-0.9945391869010969</v>
       </c>
     </row>
     <row r="75">
@@ -2374,19 +2374,19 @@
         </is>
       </c>
       <c r="C75">
-        <v>-1.347282837653495</v>
+        <v>-1.347282837653496</v>
       </c>
       <c r="D75">
-        <v>0.01850465991563272</v>
+        <v>0.01850465991563238</v>
       </c>
       <c r="E75">
-        <v>-0.428369698365174</v>
+        <v>-0.428369698365176</v>
       </c>
       <c r="F75">
-        <v>-0.4674494121341187</v>
+        <v>-0.4674494121341126</v>
       </c>
       <c r="G75">
-        <v>-0.5145787758434039</v>
+        <v>-0.5145787758434087</v>
       </c>
     </row>
     <row r="76">
@@ -2401,19 +2401,19 @@
         </is>
       </c>
       <c r="C76">
-        <v>-2.250474941242052</v>
+        <v>-2.250474941242053</v>
       </c>
       <c r="D76">
-        <v>-0.04962549765973234</v>
+        <v>-0.04962549765973312</v>
       </c>
       <c r="E76">
-        <v>0.252660722106298</v>
+        <v>0.2526607221062992</v>
       </c>
       <c r="F76">
-        <v>0.525526254414047</v>
+        <v>0.5255262544140489</v>
       </c>
       <c r="G76">
-        <v>0.03307112228652239</v>
+        <v>0.03307112228652215</v>
       </c>
     </row>
     <row r="77">
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="C77">
-        <v>0.3782071357339192</v>
+        <v>0.3782071357339202</v>
       </c>
       <c r="D77">
-        <v>-1.350462058435595</v>
+        <v>-1.350462058435593</v>
       </c>
       <c r="E77">
-        <v>-0.9018871947070721</v>
+        <v>-0.9018871947070664</v>
       </c>
       <c r="F77">
-        <v>1.872013755375333</v>
+        <v>1.872013755375335</v>
       </c>
       <c r="G77">
-        <v>-0.0473390256638196</v>
+        <v>-0.04733902566380972</v>
       </c>
     </row>
     <row r="78">
@@ -2455,19 +2455,19 @@
         </is>
       </c>
       <c r="C78">
-        <v>2.874503243344827</v>
+        <v>2.874503243344829</v>
       </c>
       <c r="D78">
-        <v>-1.328372482099162</v>
+        <v>-1.328372482099158</v>
       </c>
       <c r="E78">
-        <v>-1.297718702076707</v>
+        <v>-1.29771870207671</v>
       </c>
       <c r="F78">
-        <v>-0.6502424679549772</v>
+        <v>-0.6502424679549611</v>
       </c>
       <c r="G78">
-        <v>-1.740128316761756</v>
+        <v>-1.74012831676176</v>
       </c>
     </row>
     <row r="79">
@@ -2482,19 +2482,19 @@
         </is>
       </c>
       <c r="C79">
-        <v>-1.793011864211066</v>
+        <v>-1.793011864211064</v>
       </c>
       <c r="D79">
-        <v>-0.6507124894564532</v>
+        <v>-0.6507124894564529</v>
       </c>
       <c r="E79">
-        <v>0.2856860135503861</v>
+        <v>0.2856860135503848</v>
       </c>
       <c r="F79">
-        <v>-0.5832125433506246</v>
+        <v>-0.5832125433506337</v>
       </c>
       <c r="G79">
-        <v>1.410982212784178</v>
+        <v>1.410982212784177</v>
       </c>
     </row>
     <row r="80">
@@ -2509,19 +2509,19 @@
         </is>
       </c>
       <c r="C80">
-        <v>1.298927899775812</v>
+        <v>1.298927899775814</v>
       </c>
       <c r="D80">
-        <v>-2.022436701525638</v>
+        <v>-2.022436701525637</v>
       </c>
       <c r="E80">
-        <v>0.9955286745026259</v>
+        <v>0.9955286745026274</v>
       </c>
       <c r="F80">
-        <v>0.8010567597474884</v>
+        <v>0.8010567597474783</v>
       </c>
       <c r="G80">
-        <v>0.1849451621661236</v>
+        <v>0.1849451621661338</v>
       </c>
     </row>
     <row r="81">
@@ -2536,19 +2536,19 @@
         </is>
       </c>
       <c r="C81">
-        <v>-0.6815667119151795</v>
+        <v>-0.6815667119151805</v>
       </c>
       <c r="D81">
-        <v>1.987623119700561</v>
+        <v>1.987623119700559</v>
       </c>
       <c r="E81">
-        <v>0.9667632334811929</v>
+        <v>0.9667632334811935</v>
       </c>
       <c r="F81">
-        <v>-0.7227981325416589</v>
+        <v>-0.7227981325416616</v>
       </c>
       <c r="G81">
-        <v>-0.3791976585065948</v>
+        <v>-0.3791976585065963</v>
       </c>
     </row>
     <row r="82">
@@ -2566,16 +2566,16 @@
         <v>-1.014448871370443</v>
       </c>
       <c r="D82">
-        <v>0.1204873821406741</v>
+        <v>0.1204873821406736</v>
       </c>
       <c r="E82">
-        <v>0.4230705783261948</v>
+        <v>0.4230705783261968</v>
       </c>
       <c r="F82">
-        <v>0.4358831255885717</v>
+        <v>0.4358831255885708</v>
       </c>
       <c r="G82">
-        <v>-0.2643582674577731</v>
+        <v>-0.2643582674577701</v>
       </c>
     </row>
     <row r="83">
@@ -2590,16 +2590,16 @@
         </is>
       </c>
       <c r="C83">
-        <v>-0.3418560265363365</v>
+        <v>-0.3418560265363391</v>
       </c>
       <c r="D83">
-        <v>2.529492748422714</v>
+        <v>2.529492748422711</v>
       </c>
       <c r="E83">
-        <v>1.560870724711419</v>
+        <v>1.560870724711421</v>
       </c>
       <c r="F83">
-        <v>0.2654171277790018</v>
+        <v>0.2654171277790091</v>
       </c>
       <c r="G83">
         <v>-2.089410420537202</v>
@@ -2617,19 +2617,19 @@
         </is>
       </c>
       <c r="C84">
-        <v>-0.5628953454931476</v>
+        <v>-0.5628953454931495</v>
       </c>
       <c r="D84">
-        <v>2.160142222729005</v>
+        <v>2.160142222729004</v>
       </c>
       <c r="E84">
-        <v>0.3537643012064248</v>
+        <v>0.353764301206429</v>
       </c>
       <c r="F84">
-        <v>0.4782999192748744</v>
+        <v>0.47829991927488</v>
       </c>
       <c r="G84">
-        <v>-1.212104622059575</v>
+        <v>-1.212104622059572</v>
       </c>
     </row>
     <row r="85">
@@ -2644,19 +2644,19 @@
         </is>
       </c>
       <c r="C85">
-        <v>0.290279134709128</v>
+        <v>0.2902791347091272</v>
       </c>
       <c r="D85">
-        <v>1.156149395278498</v>
+        <v>1.156149395278499</v>
       </c>
       <c r="E85">
-        <v>-0.891778788629174</v>
+        <v>-0.8917787886291718</v>
       </c>
       <c r="F85">
-        <v>0.1675639940182692</v>
+        <v>0.167563994018278</v>
       </c>
       <c r="G85">
-        <v>-1.409390641276011</v>
+        <v>-1.40939064127601</v>
       </c>
     </row>
     <row r="86">
@@ -2674,16 +2674,16 @@
         <v>6.294881271988396</v>
       </c>
       <c r="D86">
-        <v>-0.2102234584064307</v>
+        <v>-0.2102234584064258</v>
       </c>
       <c r="E86">
-        <v>-1.082764123108113</v>
+        <v>-1.082764123108117</v>
       </c>
       <c r="F86">
-        <v>-1.217591049402718</v>
+        <v>-1.217591049402707</v>
       </c>
       <c r="G86">
-        <v>0.2847842685408727</v>
+        <v>0.2847842685408603</v>
       </c>
     </row>
     <row r="87">
@@ -2701,16 +2701,16 @@
         <v>-1.503884215717021</v>
       </c>
       <c r="D87">
-        <v>-0.6741407963832483</v>
+        <v>-0.6741407963832506</v>
       </c>
       <c r="E87">
-        <v>2.242872536141285</v>
+        <v>2.24287253614128</v>
       </c>
       <c r="F87">
-        <v>-0.9575107047449559</v>
+        <v>-0.9575107047449587</v>
       </c>
       <c r="G87">
-        <v>0.04375463405090585</v>
+        <v>0.04375463405089797</v>
       </c>
     </row>
     <row r="88">
@@ -2725,19 +2725,19 @@
         </is>
       </c>
       <c r="C88">
-        <v>0.3561074875971665</v>
+        <v>0.3561074875971634</v>
       </c>
       <c r="D88">
-        <v>4.36926744248686</v>
+        <v>4.369267442486858</v>
       </c>
       <c r="E88">
-        <v>-0.9949961815369993</v>
+        <v>-0.994996181536993</v>
       </c>
       <c r="F88">
-        <v>0.2489178400356504</v>
+        <v>0.248917840035657</v>
       </c>
       <c r="G88">
-        <v>-0.8386362447140778</v>
+        <v>-0.8386362447140757</v>
       </c>
     </row>
     <row r="89">
@@ -2755,16 +2755,16 @@
         <v>0.1472257429872214</v>
       </c>
       <c r="D89">
-        <v>-0.0625897276199093</v>
+        <v>-0.06258972761990866</v>
       </c>
       <c r="E89">
-        <v>-0.4986104759993191</v>
+        <v>-0.4986104759993135</v>
       </c>
       <c r="F89">
-        <v>1.512021491343597</v>
+        <v>1.512021491343598</v>
       </c>
       <c r="G89">
-        <v>0.03458956173507424</v>
+        <v>0.03458956173508243</v>
       </c>
     </row>
     <row r="90">
@@ -2779,19 +2779,19 @@
         </is>
       </c>
       <c r="C90">
-        <v>-0.2973745235023204</v>
+        <v>-0.297374523502319</v>
       </c>
       <c r="D90">
-        <v>-1.508745939764073</v>
+        <v>-1.508745939764071</v>
       </c>
       <c r="E90">
-        <v>-0.468420675495953</v>
+        <v>-0.4684206754959505</v>
       </c>
       <c r="F90">
-        <v>0.9755937796218238</v>
+        <v>0.9755937796218214</v>
       </c>
       <c r="G90">
-        <v>-0.1048154848957525</v>
+        <v>-0.1048154848957446</v>
       </c>
     </row>
     <row r="91">
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="C91">
-        <v>-1.310340631087811</v>
+        <v>-1.31034063108781</v>
       </c>
       <c r="D91">
-        <v>-0.9356674198092618</v>
+        <v>-0.9356674198092609</v>
       </c>
       <c r="E91">
-        <v>-0.4550722582597945</v>
+        <v>-0.455072258259798</v>
       </c>
       <c r="F91">
-        <v>-0.9647559293945682</v>
+        <v>-0.9647559293945687</v>
       </c>
       <c r="G91">
-        <v>0.1340204634726962</v>
+        <v>0.1340204634726923</v>
       </c>
     </row>
     <row r="92">
@@ -2836,16 +2836,16 @@
         <v>-1.367874463717814</v>
       </c>
       <c r="D92">
-        <v>-0.4047267373083316</v>
+        <v>-0.4047267373083307</v>
       </c>
       <c r="E92">
-        <v>-1.563020347824544</v>
+        <v>-1.563020347824547</v>
       </c>
       <c r="F92">
-        <v>-0.7382465690162844</v>
+        <v>-0.7382465690162688</v>
       </c>
       <c r="G92">
-        <v>-1.307064406883525</v>
+        <v>-1.307064406883532</v>
       </c>
     </row>
     <row r="93">
@@ -2860,19 +2860,19 @@
         </is>
       </c>
       <c r="C93">
-        <v>1.242334434215819</v>
+        <v>1.242334434215817</v>
       </c>
       <c r="D93">
-        <v>0.7691379713503511</v>
+        <v>0.7691379713503491</v>
       </c>
       <c r="E93">
-        <v>0.06951681978923574</v>
+        <v>0.06951681978923757</v>
       </c>
       <c r="F93">
-        <v>0.7988626176181309</v>
+        <v>0.7988626176181214</v>
       </c>
       <c r="G93">
-        <v>1.452502725305261</v>
+        <v>1.452502725305264</v>
       </c>
     </row>
     <row r="94">
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="C94">
-        <v>-0.2138047427388277</v>
+        <v>-0.2138047427388265</v>
       </c>
       <c r="D94">
-        <v>-1.262230704085765</v>
+        <v>-1.262230704085767</v>
       </c>
       <c r="E94">
-        <v>2.083893646933865</v>
+        <v>2.083893646933862</v>
       </c>
       <c r="F94">
-        <v>-0.297394489152983</v>
+        <v>-0.2973944891529899</v>
       </c>
       <c r="G94">
-        <v>-0.3412429642140028</v>
+        <v>-0.3412429642140019</v>
       </c>
     </row>
     <row r="95">
@@ -2917,16 +2917,16 @@
         <v>-1.144888854429891</v>
       </c>
       <c r="D95">
-        <v>-1.186925743665634</v>
+        <v>-1.186925743665633</v>
       </c>
       <c r="E95">
-        <v>-0.7651870394836792</v>
+        <v>-0.7651870394836835</v>
       </c>
       <c r="F95">
-        <v>-0.9047814801676008</v>
+        <v>-0.9047814801675989</v>
       </c>
       <c r="G95">
-        <v>0.696467501786881</v>
+        <v>0.6964675017868729</v>
       </c>
     </row>
     <row r="96">
@@ -2941,19 +2941,19 @@
         </is>
       </c>
       <c r="C96">
-        <v>-0.5566311857966587</v>
+        <v>-0.5566311857966589</v>
       </c>
       <c r="D96">
-        <v>0.4000726625716033</v>
+        <v>0.400072662571604</v>
       </c>
       <c r="E96">
-        <v>-2.038134016506414</v>
+        <v>-2.038134016506416</v>
       </c>
       <c r="F96">
-        <v>-0.9921293284648472</v>
+        <v>-0.9921293284648355</v>
       </c>
       <c r="G96">
-        <v>-0.8189333332009389</v>
+        <v>-0.8189333332009445</v>
       </c>
     </row>
     <row r="97">
@@ -2968,19 +2968,19 @@
         </is>
       </c>
       <c r="C97">
-        <v>0.5317654047652414</v>
+        <v>0.531765404765242</v>
       </c>
       <c r="D97">
-        <v>0.4340536536287134</v>
+        <v>0.4340536536287122</v>
       </c>
       <c r="E97">
-        <v>1.438110914112046</v>
+        <v>1.438110914112045</v>
       </c>
       <c r="F97">
-        <v>-0.6960400764383233</v>
+        <v>-0.6960400764383249</v>
       </c>
       <c r="G97">
-        <v>-0.8866041705247046</v>
+        <v>-0.886604170524705</v>
       </c>
     </row>
     <row r="98">
@@ -2995,19 +2995,19 @@
         </is>
       </c>
       <c r="C98">
-        <v>-1.444945685148498</v>
+        <v>-1.444945685148497</v>
       </c>
       <c r="D98">
-        <v>-1.483945712608207</v>
+        <v>-1.483945712608204</v>
       </c>
       <c r="E98">
         <v>-1.066107672279164</v>
       </c>
       <c r="F98">
-        <v>0.2239122877537955</v>
+        <v>0.2239122877537972</v>
       </c>
       <c r="G98">
-        <v>0.573322188464657</v>
+        <v>0.5733221884646558</v>
       </c>
     </row>
     <row r="99">
@@ -3022,19 +3022,19 @@
         </is>
       </c>
       <c r="C99">
-        <v>-0.6707922848841339</v>
+        <v>-0.6707922848841327</v>
       </c>
       <c r="D99">
-        <v>-0.9380971137238684</v>
+        <v>-0.9380971137238667</v>
       </c>
       <c r="E99">
-        <v>-1.415234160154332</v>
+        <v>-1.415234160154336</v>
       </c>
       <c r="F99">
-        <v>-1.187981590238663</v>
+        <v>-1.187981590238655</v>
       </c>
       <c r="G99">
-        <v>-0.6691511196254571</v>
+        <v>-0.6691511196254629</v>
       </c>
     </row>
     <row r="100">
@@ -3049,19 +3049,19 @@
         </is>
       </c>
       <c r="C100">
-        <v>0.2084415727833063</v>
+        <v>0.208441572783306</v>
       </c>
       <c r="D100">
-        <v>0.0731774789438185</v>
+        <v>0.07317747894381804</v>
       </c>
       <c r="E100">
-        <v>0.5905990783655448</v>
+        <v>0.5905990783655473</v>
       </c>
       <c r="F100">
-        <v>0.7976663754152787</v>
+        <v>0.7976663754152757</v>
       </c>
       <c r="G100">
-        <v>0.09786760047198921</v>
+        <v>0.09786760047199303</v>
       </c>
     </row>
     <row r="101">
@@ -3076,19 +3076,19 @@
         </is>
       </c>
       <c r="C101">
-        <v>1.841065576045219</v>
+        <v>1.841065576045222</v>
       </c>
       <c r="D101">
-        <v>-1.908251108931595</v>
+        <v>-1.908251108931592</v>
       </c>
       <c r="E101">
-        <v>-1.155855010176348</v>
+        <v>-1.15585501017635</v>
       </c>
       <c r="F101">
-        <v>-0.3052487865494327</v>
+        <v>-0.3052487865494258</v>
       </c>
       <c r="G101">
-        <v>-0.5785032831936491</v>
+        <v>-0.5785032831936496</v>
       </c>
     </row>
     <row r="102">
@@ -3103,19 +3103,19 @@
         </is>
       </c>
       <c r="C102">
-        <v>0.8804462561788076</v>
+        <v>0.8804462561788069</v>
       </c>
       <c r="D102">
-        <v>-0.09578423444273602</v>
+        <v>-0.09578423444273608</v>
       </c>
       <c r="E102">
-        <v>-0.5744694211849498</v>
+        <v>-0.5744694211849458</v>
       </c>
       <c r="F102">
-        <v>1.523818399109826</v>
+        <v>1.523818399109822</v>
       </c>
       <c r="G102">
-        <v>1.306865419971859</v>
+        <v>1.306865419971863</v>
       </c>
     </row>
     <row r="103">
@@ -3130,19 +3130,19 @@
         </is>
       </c>
       <c r="C103">
-        <v>-0.3441618133009812</v>
+        <v>-0.3441618133009813</v>
       </c>
       <c r="D103">
-        <v>0.2649055510884686</v>
+        <v>0.2649055510884685</v>
       </c>
       <c r="E103">
-        <v>-0.03946386019907672</v>
+        <v>-0.03946386019907296</v>
       </c>
       <c r="F103">
-        <v>0.8831473351266624</v>
+        <v>0.8831473351266617</v>
       </c>
       <c r="G103">
-        <v>-0.2124741774640011</v>
+        <v>-0.212474177463995</v>
       </c>
     </row>
     <row r="104">
@@ -3157,19 +3157,19 @@
         </is>
       </c>
       <c r="C104">
-        <v>0.1566261911307401</v>
+        <v>0.1566261911307403</v>
       </c>
       <c r="D104">
-        <v>-0.1888881033488207</v>
+        <v>-0.1888881033488208</v>
       </c>
       <c r="E104">
-        <v>-0.5601379506532915</v>
+        <v>-0.5601379506532913</v>
       </c>
       <c r="F104">
-        <v>0.2158793228800918</v>
+        <v>0.2158793228800848</v>
       </c>
       <c r="G104">
-        <v>1.332764559566275</v>
+        <v>1.332764559566276</v>
       </c>
     </row>
     <row r="105">
@@ -3184,19 +3184,19 @@
         </is>
       </c>
       <c r="C105">
-        <v>3.763329635337496</v>
+        <v>3.763329635337499</v>
       </c>
       <c r="D105">
-        <v>-1.165484803325804</v>
+        <v>-1.165484803325801</v>
       </c>
       <c r="E105">
-        <v>-0.9564433620869</v>
+        <v>-0.9564433620869001</v>
       </c>
       <c r="F105">
-        <v>0.1448947692330343</v>
+        <v>0.1448947692330405</v>
       </c>
       <c r="G105">
-        <v>-0.7673850039152114</v>
+        <v>-0.7673850039152086</v>
       </c>
     </row>
     <row r="106">
@@ -3211,19 +3211,19 @@
         </is>
       </c>
       <c r="C106">
-        <v>-0.4896397984084288</v>
+        <v>-0.4896397984084309</v>
       </c>
       <c r="D106">
-        <v>2.364994133096923</v>
+        <v>2.364994133096922</v>
       </c>
       <c r="E106">
-        <v>0.2175777267180214</v>
+        <v>0.2175777267180257</v>
       </c>
       <c r="F106">
-        <v>0.3105907581994289</v>
+        <v>0.3105907581994355</v>
       </c>
       <c r="G106">
-        <v>-1.357438522284835</v>
+        <v>-1.357438522284834</v>
       </c>
     </row>
     <row r="107">
@@ -3238,19 +3238,19 @@
         </is>
       </c>
       <c r="C107">
-        <v>-0.7136162284628483</v>
+        <v>-0.7136162284628474</v>
       </c>
       <c r="D107">
-        <v>-0.3312447139765892</v>
+        <v>-0.3312447139765879</v>
       </c>
       <c r="E107">
-        <v>-1.511782278301426</v>
+        <v>-1.511782278301431</v>
       </c>
       <c r="F107">
-        <v>-1.686974629638171</v>
+        <v>-1.686974629638162</v>
       </c>
       <c r="G107">
-        <v>-0.6104620741640552</v>
+        <v>-0.6104620741640635</v>
       </c>
     </row>
     <row r="108">
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C108">
-        <v>0.8923293204519824</v>
+        <v>0.8923293204519832</v>
       </c>
       <c r="D108">
-        <v>-0.2436828377262041</v>
+        <v>-0.2436828377262042</v>
       </c>
       <c r="E108">
-        <v>0.5376940042966434</v>
+        <v>0.5376940042966435</v>
       </c>
       <c r="F108">
-        <v>-0.01959915952089994</v>
+        <v>-0.01959915952090505</v>
       </c>
       <c r="G108">
-        <v>0.08622139927386246</v>
+        <v>0.08622139927386509</v>
       </c>
     </row>
     <row r="109">
@@ -3292,19 +3292,19 @@
         </is>
       </c>
       <c r="C109">
-        <v>0.1021047574206214</v>
+        <v>0.1021047574206217</v>
       </c>
       <c r="D109">
-        <v>-0.0001507181617934892</v>
+        <v>-0.0001507181617940168</v>
       </c>
       <c r="E109">
-        <v>0.5263889296557698</v>
+        <v>0.5263889296557717</v>
       </c>
       <c r="F109">
-        <v>0.4877500768706691</v>
+        <v>0.4877500768706672</v>
       </c>
       <c r="G109">
-        <v>-0.1554202489462231</v>
+        <v>-0.1554202489462191</v>
       </c>
     </row>
     <row r="110">
@@ -3322,16 +3322,16 @@
         <v>-1.572290709342799</v>
       </c>
       <c r="D110">
-        <v>0.09180061218018669</v>
+        <v>0.09180061218018606</v>
       </c>
       <c r="E110">
-        <v>-0.1014060474746434</v>
+        <v>-0.1014060474746443</v>
       </c>
       <c r="F110">
-        <v>-0.4201277344956423</v>
+        <v>-0.4201277344956408</v>
       </c>
       <c r="G110">
-        <v>0.2914601076015075</v>
+        <v>0.2914601076015036</v>
       </c>
     </row>
     <row r="111">
@@ -3346,19 +3346,19 @@
         </is>
       </c>
       <c r="C111">
-        <v>1.958774664623959</v>
+        <v>1.958774664623961</v>
       </c>
       <c r="D111">
-        <v>-1.292239991392536</v>
+        <v>-1.292239991392538</v>
       </c>
       <c r="E111">
-        <v>2.007584982819913</v>
+        <v>2.007584982819909</v>
       </c>
       <c r="F111">
-        <v>-0.4876396199433221</v>
+        <v>-0.4876396199433407</v>
       </c>
       <c r="G111">
-        <v>1.048708975404642</v>
+        <v>1.048708975404646</v>
       </c>
     </row>
     <row r="112">
@@ -3373,19 +3373,19 @@
         </is>
       </c>
       <c r="C112">
-        <v>0.4545265782018878</v>
+        <v>0.4545265782018872</v>
       </c>
       <c r="D112">
-        <v>-0.05606355344366089</v>
+        <v>-0.05606355344366265</v>
       </c>
       <c r="E112">
-        <v>0.4834445000858114</v>
+        <v>0.4834445000858174</v>
       </c>
       <c r="F112">
-        <v>2.114592906538217</v>
+        <v>2.114592906538208</v>
       </c>
       <c r="G112">
-        <v>0.3314242633193628</v>
+        <v>0.3314242633193762</v>
       </c>
     </row>
     <row r="113">
@@ -3400,19 +3400,19 @@
         </is>
       </c>
       <c r="C113">
-        <v>-0.2747411743803822</v>
+        <v>-0.2747411743803816</v>
       </c>
       <c r="D113">
         <v>-1.39541499813655</v>
       </c>
       <c r="E113">
-        <v>1.462643140235152</v>
+        <v>1.462643140235153</v>
       </c>
       <c r="F113">
-        <v>0.882102328338628</v>
+        <v>0.8821023283386252</v>
       </c>
       <c r="G113">
-        <v>-0.8405874050898529</v>
+        <v>-0.8405874050898475</v>
       </c>
     </row>
     <row r="114">
@@ -3427,19 +3427,19 @@
         </is>
       </c>
       <c r="C114">
-        <v>-1.932955601589625</v>
+        <v>-1.932955601589624</v>
       </c>
       <c r="D114">
-        <v>0.01047029167201013</v>
+        <v>0.01047029167200975</v>
       </c>
       <c r="E114">
-        <v>-0.5372828840276206</v>
+        <v>-0.5372828840276216</v>
       </c>
       <c r="F114">
-        <v>-0.4170080343729877</v>
+        <v>-0.4170080343729872</v>
       </c>
       <c r="G114">
-        <v>0.3266622904837742</v>
+        <v>0.3266622904837715</v>
       </c>
     </row>
     <row r="115">
@@ -3454,19 +3454,19 @@
         </is>
       </c>
       <c r="C115">
-        <v>-0.6385003726964879</v>
+        <v>-0.6385003726964881</v>
       </c>
       <c r="D115">
         <v>-1.185775301180606</v>
       </c>
       <c r="E115">
-        <v>0.02567530906699437</v>
+        <v>0.02567530906699697</v>
       </c>
       <c r="F115">
-        <v>1.541787021743588</v>
+        <v>1.541787021743586</v>
       </c>
       <c r="G115">
-        <v>0.5852098366297741</v>
+        <v>0.5852098366297791</v>
       </c>
     </row>
     <row r="116">
@@ -3484,16 +3484,16 @@
         <v>-1.388281976641699</v>
       </c>
       <c r="D116">
-        <v>0.8399125895198886</v>
+        <v>0.8399125895198887</v>
       </c>
       <c r="E116">
-        <v>-0.8157171247371101</v>
+        <v>-0.8157171247371092</v>
       </c>
       <c r="F116">
-        <v>-0.7236161696143785</v>
+        <v>-0.7236161696143807</v>
       </c>
       <c r="G116">
-        <v>0.5655439337055205</v>
+        <v>0.5655439337055203</v>
       </c>
     </row>
     <row r="117">
@@ -3508,19 +3508,19 @@
         </is>
       </c>
       <c r="C117">
-        <v>-1.701813689690222</v>
+        <v>-1.701813689690223</v>
       </c>
       <c r="D117">
-        <v>-0.04856378654593768</v>
+        <v>-0.04856378654593824</v>
       </c>
       <c r="E117">
-        <v>-0.3240329054458148</v>
+        <v>-0.3240329054458146</v>
       </c>
       <c r="F117">
-        <v>0.04960617517700046</v>
+        <v>0.04960617517699931</v>
       </c>
       <c r="G117">
-        <v>0.8038680946945322</v>
+        <v>0.8038680946945305</v>
       </c>
     </row>
     <row r="118">
@@ -3538,16 +3538,16 @@
         <v>0.5921999798756796</v>
       </c>
       <c r="D118">
-        <v>-0.5987984822862761</v>
+        <v>-0.5987984822862787</v>
       </c>
       <c r="E118">
-        <v>1.721663636263004</v>
+        <v>1.721663636263003</v>
       </c>
       <c r="F118">
-        <v>0.3139480904104335</v>
+        <v>0.313948090410425</v>
       </c>
       <c r="G118">
-        <v>0.1291758573768862</v>
+        <v>0.1291758573768891</v>
       </c>
     </row>
     <row r="119">
@@ -3562,19 +3562,19 @@
         </is>
       </c>
       <c r="C119">
-        <v>-0.07905691626221933</v>
+        <v>-0.07905691626222036</v>
       </c>
       <c r="D119">
-        <v>1.698897221505476</v>
+        <v>1.698897221505475</v>
       </c>
       <c r="E119">
-        <v>0.6613788424831157</v>
+        <v>0.6613788424831184</v>
       </c>
       <c r="F119">
-        <v>-0.04815937774236116</v>
+        <v>-0.04815937774236109</v>
       </c>
       <c r="G119">
-        <v>-0.4512729388221925</v>
+        <v>-0.4512729388221915</v>
       </c>
     </row>
     <row r="120">
@@ -3589,19 +3589,19 @@
         </is>
       </c>
       <c r="C120">
-        <v>0.2579463620738205</v>
+        <v>0.25794636207382</v>
       </c>
       <c r="D120">
-        <v>-0.3230159894612841</v>
+        <v>-0.3230159894612845</v>
       </c>
       <c r="E120">
-        <v>0.1841519702709347</v>
+        <v>0.1841519702709391</v>
       </c>
       <c r="F120">
         <v>1.685712246154684</v>
       </c>
       <c r="G120">
-        <v>-0.1850644201402051</v>
+        <v>-0.1850644201401975</v>
       </c>
     </row>
     <row r="121">
@@ -3619,16 +3619,16 @@
         <v>-2.974325483809729</v>
       </c>
       <c r="D121">
-        <v>-0.574301629189414</v>
+        <v>-0.5743016291894134</v>
       </c>
       <c r="E121">
-        <v>-1.530637826028969</v>
+        <v>-1.530637826028967</v>
       </c>
       <c r="F121">
-        <v>0.5808694935781848</v>
+        <v>0.5808694935781881</v>
       </c>
       <c r="G121">
-        <v>0.5015898109830548</v>
+        <v>0.5015898109830553</v>
       </c>
     </row>
     <row r="122">
@@ -3643,19 +3643,19 @@
         </is>
       </c>
       <c r="C122">
-        <v>-0.6379701582532945</v>
+        <v>-0.6379701582532953</v>
       </c>
       <c r="D122">
-        <v>0.3192910868662933</v>
+        <v>0.3192910868662935</v>
       </c>
       <c r="E122">
-        <v>-0.4392537037801517</v>
+        <v>-0.4392537037801463</v>
       </c>
       <c r="F122">
-        <v>1.432645003322425</v>
+        <v>1.432645003322426</v>
       </c>
       <c r="G122">
-        <v>0.1899284159685849</v>
+        <v>0.1899284159685909</v>
       </c>
     </row>
     <row r="123">
@@ -3670,19 +3670,19 @@
         </is>
       </c>
       <c r="C123">
-        <v>0.3402316582631112</v>
+        <v>0.3402316582631122</v>
       </c>
       <c r="D123">
-        <v>0.4393692268482598</v>
+        <v>0.4393692268482596</v>
       </c>
       <c r="E123">
-        <v>0.6348883269595288</v>
+        <v>0.6348883269595251</v>
       </c>
       <c r="F123">
-        <v>-1.738568814942034</v>
+        <v>-1.738568814942039</v>
       </c>
       <c r="G123">
-        <v>0.6936061760470611</v>
+        <v>0.6936061760470542</v>
       </c>
     </row>
     <row r="124">
@@ -3697,19 +3697,19 @@
         </is>
       </c>
       <c r="C124">
-        <v>-1.185535340717318</v>
+        <v>-1.185535340717319</v>
       </c>
       <c r="D124">
         <v>0.6445657387352268</v>
       </c>
       <c r="E124">
-        <v>-0.7491024617550431</v>
+        <v>-0.7491024617550364</v>
       </c>
       <c r="F124">
-        <v>1.540352535699412</v>
+        <v>1.540352535699413</v>
       </c>
       <c r="G124">
-        <v>0.08912090466321207</v>
+        <v>0.08912090466322078</v>
       </c>
     </row>
     <row r="125">
@@ -3727,16 +3727,16 @@
         <v>-1.844538749193731</v>
       </c>
       <c r="D125">
-        <v>0.2437624388066799</v>
+        <v>0.2437624388066789</v>
       </c>
       <c r="E125">
-        <v>0.5591102064396846</v>
+        <v>0.5591102064396842</v>
       </c>
       <c r="F125">
-        <v>-0.185817782463898</v>
+        <v>-0.1858177824638976</v>
       </c>
       <c r="G125">
-        <v>-0.3185822665935001</v>
+        <v>-0.318582266593502</v>
       </c>
     </row>
     <row r="126">
@@ -3751,19 +3751,19 @@
         </is>
       </c>
       <c r="C126">
-        <v>-0.910122203241375</v>
+        <v>-0.9101222032413757</v>
       </c>
       <c r="D126">
-        <v>0.6008813926505319</v>
+        <v>0.6008813926505311</v>
       </c>
       <c r="E126">
-        <v>0.1147129675196087</v>
+        <v>0.1147129675196108</v>
       </c>
       <c r="F126">
-        <v>0.376212948583208</v>
+        <v>0.3762129485832055</v>
       </c>
       <c r="G126">
-        <v>0.475899209517439</v>
+        <v>0.4758992095174402</v>
       </c>
     </row>
   </sheetData>
